--- a/wynik_rr.xlsx
+++ b/wynik_rr.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="63">
   <si>
     <t>strona</t>
   </si>
@@ -101,9 +101,6 @@
   </si>
   <si>
     <t>PODZIEMIA POŁUDNIOWE</t>
-  </si>
-  <si>
-    <t>ta karta musi byc tak odwrocona|jezeli posiadlosc|jest zastawiona</t>
   </si>
   <si>
     <t>07</t>
@@ -757,7 +754,7 @@
         <v>200</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1"/>
       <c r="L4" t="s">
@@ -775,19 +772,19 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D5" s="1">
         <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
         <v>19</v>
@@ -819,19 +816,19 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="D6" s="1">
         <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
         <v>19</v>
@@ -869,13 +866,13 @@
         <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1">
         <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
         <v>19</v>
@@ -908,13 +905,13 @@
         <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1">
         <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
         <v>19</v>
@@ -952,13 +949,13 @@
         <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1">
         <v>150</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1"/>
       <c r="L9" t="s">
@@ -982,13 +979,13 @@
         <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1">
         <v>160</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -1026,13 +1023,13 @@
         <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" s="1">
         <v>200</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G11" s="1"/>
       <c r="L11" t="s">
@@ -1056,13 +1053,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1">
         <v>180</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
         <v>19</v>
@@ -1100,13 +1097,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D13" s="1">
         <v>180</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>19</v>
@@ -1144,13 +1141,13 @@
         <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1">
         <v>200</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
         <v>19</v>
@@ -1188,13 +1185,13 @@
         <v>16</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" s="1">
         <v>220</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
         <v>19</v>
@@ -1232,13 +1229,13 @@
         <v>16</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="1">
         <v>220</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
         <v>19</v>
@@ -1276,13 +1273,13 @@
         <v>16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="1">
         <v>240</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
         <v>19</v>
@@ -1320,13 +1317,13 @@
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1">
         <v>200</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G18" s="1"/>
       <c r="L18" t="s">
@@ -1350,13 +1347,13 @@
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="1">
         <v>260</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
         <v>19</v>
@@ -1394,13 +1391,13 @@
         <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="1">
         <v>260</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
         <v>19</v>
@@ -1438,13 +1435,13 @@
         <v>16</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="1">
         <v>150</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G21" s="1"/>
       <c r="L21" t="s">
@@ -1468,13 +1465,13 @@
         <v>16</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" s="1">
         <v>280</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
         <v>19</v>
@@ -1512,13 +1509,13 @@
         <v>16</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="1">
         <v>300</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F23" t="s">
         <v>19</v>
@@ -1556,13 +1553,13 @@
         <v>16</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="1">
         <v>300</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F24" t="s">
         <v>19</v>
@@ -1600,13 +1597,13 @@
         <v>16</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="1">
         <v>320</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
         <v>19</v>
@@ -1644,13 +1641,13 @@
         <v>16</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="1">
         <v>200</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G26" s="1"/>
       <c r="L26" t="s">
@@ -1674,13 +1671,13 @@
         <v>16</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" s="1">
         <v>340</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F27" t="s">
         <v>19</v>
@@ -1718,13 +1715,13 @@
         <v>16</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="1">
         <v>340</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
         <v>19</v>
@@ -1762,13 +1759,13 @@
         <v>16</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="1">
         <v>360</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F29" t="s">
         <v>19</v>
@@ -1806,13 +1803,13 @@
         <v>16</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" s="1">
         <v>380</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F30" t="s">
         <v>19</v>
@@ -1850,13 +1847,13 @@
         <v>16</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D31" s="1">
         <v>150</v>
       </c>
       <c r="E31" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G31" s="1"/>
       <c r="L31" t="s">
@@ -1880,13 +1877,13 @@
         <v>16</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D32" s="1">
         <v>400</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F32" t="s">
         <v>19</v>
@@ -1924,13 +1921,13 @@
         <v>16</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="1">
         <v>200</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G33" s="1"/>
       <c r="L33" t="s">
@@ -1954,13 +1951,13 @@
         <v>16</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D34" s="1">
         <v>450</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F34" t="s">
         <v>19</v>
@@ -1998,13 +1995,13 @@
         <v>16</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D35" s="1">
         <v>500</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F35" t="s">
         <v>19</v>
